--- a/inputs/tested/7268/output/normalized_review.xlsx
+++ b/inputs/tested/7268/output/normalized_review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X112"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -495,65 +495,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SOFT</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>voltage</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>voltage</t>
+          <t>power_kw</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>power_kw</t>
+          <t>current_a</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>current_a</t>
+          <t>va</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>bus_protocol</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>bus_protocol</t>
+          <t>bus_naam</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>bus_naam</t>
+          <t>derden_flag</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>derden_flag</t>
+          <t>locatie</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>locatie</t>
+          <t>regelkast_spec</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>regelkast_spec</t>
+          <t>opmerking</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>opmerking</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>source_ref</t>
         </is>
@@ -562,7 +557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -589,43 +584,44 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MODbus-punten</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>MODbus</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>MODbus</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r5</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -664,32 +660,29 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r6</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -727,32 +720,29 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r7</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -790,32 +780,29 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Kvs=40</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Kvs=40</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r8</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -842,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -853,36 +840,33 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r9</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -909,50 +893,47 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="O7" t="n">
         <v>6</v>
       </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r10</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -991,32 +972,29 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r11</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1054,32 +1032,29 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r12</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1106,50 +1081,47 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="O10" t="n">
         <v>6</v>
       </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r13</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1188,32 +1160,29 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r14</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1251,32 +1220,29 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r15</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1315,32 +1281,29 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r16</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1378,32 +1341,29 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r17</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1430,50 +1390,47 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="O15" t="n">
         <v>6</v>
       </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r18</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1511,36 +1468,33 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0-10VDC/600 kPa</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0-10VDC/600 kPa</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r19</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1578,28 +1532,25 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r20</t>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1625,50 +1576,47 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
       <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
         <v>10</v>
       </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>400V/10A/4kW,Geen voeding vanuit de regelkast</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>400V/10A/4kW,Geen voeding vanuit de regelkast</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r22</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1695,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1706,36 +1654,33 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0-10VDC</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0-10VDC</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r23</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1773,35 +1718,32 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="M20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>25</v>
       </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>PDM / max 25A</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>PDM / max 25A</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r24</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1831,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1839,36 +1781,33 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>250vac wisselcontact</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>250vac wisselcontact</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r25</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1906,32 +1845,29 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r26</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1970,32 +1906,29 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r27</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2034,32 +1967,29 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="b">
-        <v>0</v>
-      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r28</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r28</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2097,32 +2027,29 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="b">
-        <v>0</v>
-      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r29</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2160,32 +2087,29 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="b">
-        <v>0</v>
-      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r30</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2212,50 +2136,47 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="O27" t="n">
         <v>6</v>
       </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="b">
-        <v>0</v>
-      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r31</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2293,36 +2214,33 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="b">
-        <v>0</v>
-      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0-10VDC/600 kPa</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0-10VDC/600 kPa</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r32</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2360,28 +2278,25 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="b">
-        <v>0</v>
-      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r33</t>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2408,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2419,36 +2334,37 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="b">
-        <v>0</v>
-      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r35</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2486,32 +2402,29 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="b">
-        <v>0</v>
-      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>DN 40</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>DN 40</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r36</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2544,41 +2457,38 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="b">
-        <v>0</v>
-      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r37</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2608,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2616,28 +2526,25 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="b">
-        <v>0</v>
-      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r38</t>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2664,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2675,36 +2582,37 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="b">
-        <v>0</v>
-      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r39</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2742,32 +2650,29 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="b">
-        <v>0</v>
-      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>DN 40</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>DN 40</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r40</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r40</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2800,41 +2705,38 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="b">
-        <v>0</v>
-      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r41</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r41</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2864,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2872,28 +2774,25 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="b">
-        <v>0</v>
-      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r42</t>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r42</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2931,32 +2830,29 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="b">
-        <v>0</v>
-      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r43</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2989,44 +2885,41 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P39" t="n">
+      <c r="O39" t="n">
         <v>6</v>
       </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="b">
-        <v>0</v>
-      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r44</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3053,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3064,36 +2957,37 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="b">
-        <v>0</v>
-      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r46</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r46</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3131,32 +3025,29 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="b">
-        <v>0</v>
-      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r47</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3189,44 +3080,41 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P42" t="n">
+      <c r="O42" t="n">
         <v>6</v>
       </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="b">
-        <v>0</v>
-      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r48</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3253,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3264,36 +3152,37 @@
       <c r="L43" t="n">
         <v>0</v>
       </c>
-      <c r="M43" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="b">
-        <v>0</v>
-      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r50</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r50</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3331,32 +3220,29 @@
       <c r="L44" t="n">
         <v>0</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="b">
-        <v>0</v>
-      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r51</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r51</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3389,44 +3275,41 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P45" t="n">
+      <c r="O45" t="n">
         <v>6</v>
       </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="b">
-        <v>0</v>
-      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r52</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r52</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3460,41 +3343,38 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="b">
-        <v>0</v>
-      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2p-24vac</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2p-24vac</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r53</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r53</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3532,36 +3412,33 @@
       <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="b">
-        <v>0</v>
-      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0-10VDC/0-500Pa</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0-10VDC/0-500Pa</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r54</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3584,50 +3461,47 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P48" t="n">
+      <c r="O48" t="n">
         <v>6</v>
       </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="b">
-        <v>0</v>
-      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r55</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r55</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3654,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3665,36 +3539,37 @@
       <c r="L49" t="n">
         <v>0</v>
       </c>
-      <c r="M49" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="b">
-        <v>0</v>
-      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r57</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3732,32 +3607,29 @@
       <c r="L50" t="n">
         <v>0</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="b">
-        <v>0</v>
-      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DN 40</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>DN 40</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r58</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r58</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3790,41 +3662,38 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="b">
-        <v>0</v>
-      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r59</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r59</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3854,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3862,28 +3731,25 @@
       <c r="L52" t="n">
         <v>0</v>
       </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="b">
-        <v>0</v>
-      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r60</t>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r60</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3910,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3921,36 +3787,37 @@
       <c r="L53" t="n">
         <v>0</v>
       </c>
-      <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="b">
-        <v>0</v>
-      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r61</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r61</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3988,32 +3855,29 @@
       <c r="L54" t="n">
         <v>0</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="b">
-        <v>0</v>
-      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>DN 40</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>DN 40</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r62</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r62</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4046,41 +3910,38 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="b">
-        <v>0</v>
-      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r63</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r63</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4110,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4118,28 +3979,25 @@
       <c r="L56" t="n">
         <v>0</v>
       </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="b">
-        <v>0</v>
-      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r64</t>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r64</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4177,32 +4035,29 @@
       <c r="L57" t="n">
         <v>0</v>
       </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="b">
-        <v>0</v>
-      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>100 mm diepe huls LGNi</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>100 mm diepe huls LGNi</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r65</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r65</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4235,44 +4090,41 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="P58" t="n">
+      <c r="O58" t="n">
         <v>6</v>
       </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="b">
-        <v>0</v>
-      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>230vac/6A</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>230vac/6A</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r66</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r66</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4302,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4310,32 +4162,29 @@
       <c r="L59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="b">
-        <v>0</v>
-      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>&lt; 5°C</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>&lt; 5°C</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r67</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r67</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4358,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -4369,39 +4218,36 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="N60" t="n">
         <v>2.2</v>
       </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="b">
-        <v>0</v>
-      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>EC,400V/2,2kW</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>EC,400V/2,2kW</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r68</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r68</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4439,32 +4285,29 @@
       <c r="L61" t="n">
         <v>0</v>
       </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="b">
-        <v>0</v>
-      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r69</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r69</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4487,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -4498,39 +4341,36 @@
       <c r="L62" t="n">
         <v>0</v>
       </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="N62" t="n">
         <v>2.2</v>
       </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="b">
-        <v>0</v>
-      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>EC,400V/2,2kW</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>EC,400V/2,2kW</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r70</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r70</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4568,36 +4408,33 @@
       <c r="L63" t="n">
         <v>0</v>
       </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="b">
-        <v>0</v>
-      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0..20ppm0..10V_24V</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>0..20ppm0..10V_24V</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r71</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r71</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4635,32 +4472,29 @@
       <c r="L64" t="n">
         <v>0</v>
       </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="b">
-        <v>0</v>
-      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r72</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4698,36 +4532,33 @@
       <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="b">
-        <v>0</v>
-      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0-10VDC/0-500Pa</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0-10VDC/0-500Pa</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r73</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r73</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4765,36 +4596,33 @@
       <c r="L66" t="n">
         <v>0</v>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="b">
-        <v>0</v>
-      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0-10VDC/0-500Pa</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>0-10VDC/0-500Pa</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r74</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r74</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4827,41 +4655,38 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="b">
-        <v>0</v>
-      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2p-24vac</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>2p-24vac</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r75</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r75</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4894,44 +4719,41 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="N68" t="n">
         <v>2.2</v>
       </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="b">
-        <v>0</v>
-      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>230V/2,2kW</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>230V/2,2kW</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r77</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r77</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4960,44 +4782,41 @@
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="N69" t="n">
         <v>2.2</v>
       </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="b">
-        <v>0</v>
-      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>400V/2,2kW</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>400V/2,2kW</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r80</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r80</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5027,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5035,28 +4854,25 @@
       <c r="L70" t="n">
         <v>0</v>
       </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="b">
-        <v>0</v>
-      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r81</t>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r81</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5089,41 +4905,38 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="b">
-        <v>0</v>
-      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r82</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r82</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5150,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5161,32 +4974,29 @@
       <c r="L72" t="n">
         <v>0</v>
       </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="b">
-        <v>0</v>
-      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r83</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r83</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5215,44 +5025,41 @@
         <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="O73" t="n">
+      <c r="N73" t="n">
         <v>2.2</v>
       </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="b">
-        <v>0</v>
-      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>400V/2,2kW</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>400V/2,2kW</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r85</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r85</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5285,41 +5092,38 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="b">
-        <v>0</v>
-      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>3p-230vac</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>3p-230vac</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r86</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r86</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5346,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -5357,32 +5161,29 @@
       <c r="L75" t="n">
         <v>0</v>
       </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="b">
-        <v>0</v>
-      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>LGNi1000</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>LGNi1000</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r87</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r87</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5412,36 +5213,33 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="b">
-        <v>0</v>
-      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r88</t>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r88</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5471,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -5479,32 +5277,29 @@
       <c r="L77" t="n">
         <v>0</v>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="b">
-        <v>0</v>
-      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Bestek 3.5.1</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Bestek 3.5.1</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r90</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r90</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5533,33 +5328,30 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="b">
-        <v>0</v>
-      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r91</t>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r91</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5597,32 +5389,33 @@
       <c r="L79" t="n">
         <v>0</v>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>MODbus-punten</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="b">
-        <v>0</v>
-      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>..kWh Schneider Modbus 485</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>..kWh Schneider Modbus 485</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r93</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5660,32 +5453,33 @@
       <c r="L80" t="n">
         <v>0</v>
       </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>MODbus-punten</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="b">
-        <v>0</v>
-      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>..kWh Schneider Modbus 485</t>
+        </is>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>..kWh Schneider Modbus 485</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r94</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r94</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5723,32 +5517,33 @@
       <c r="L81" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>MODbus-punten</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="b">
-        <v>0</v>
-      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>..kWh Schneider Modbus 485</t>
+        </is>
+      </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>..kWh Schneider Modbus 485</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r95</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r95</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5786,32 +5581,33 @@
       <c r="L82" t="n">
         <v>0</v>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>MODbus-punten</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="b">
-        <v>0</v>
-      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Kadis (incl. Modbus),..mBestek 3.3.1</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Kadis (incl. Modbus),..mBestek 3.3.1</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r96</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r96</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5849,32 +5645,29 @@
       <c r="L83" t="n">
         <v>0</v>
       </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="b">
-        <v>0</v>
-      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>..mBestek 3.3.1</t>
+        </is>
+      </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>..mBestek 3.3.1</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r97</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r97</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5912,32 +5705,33 @@
       <c r="L84" t="n">
         <v>0</v>
       </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>M-bus-punten</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="b">
-        <v>0</v>
-      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Kamstrupj / Siemens M-bus,..mBestek 3.3.2</t>
+        </is>
+      </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Kamstrupj / Siemens M-bus,..mBestek 3.3.2</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r98</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5966,37 +5760,34 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="b">
-        <v>0</v>
-      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>I.o.m. Vink Dali,Bestek 4.2.6</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>I.o.m. Vink Dali,Bestek 4.2.6</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r102</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r102</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6030,32 +5821,29 @@
       <c r="L86" t="n">
         <v>0</v>
       </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="b">
-        <v>0</v>
-      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>I.o.m. Vink Dali,Bestek 4.2.6</t>
+        </is>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>I.o.m. Vink Dali,Bestek 4.2.6</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r103</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r103</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6084,37 +5872,34 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="b">
-        <v>0</v>
-      </c>
+      <c r="S87" t="b">
+        <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Daglichtregeling via verlichtingssysteem,Bestek 4.5.2</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Daglichtregeling via verlichtingssysteem,Bestek 4.5.2</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r104</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r104</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6140,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -6148,32 +5933,29 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="b">
-        <v>0</v>
-      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Bestek 6.2.3</t>
+        </is>
+      </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Bestek 6.2.3</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r106</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r106</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6199,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -6207,32 +5989,29 @@
       <c r="L89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="b">
-        <v>0</v>
-      </c>
+      <c r="S89" t="b">
+        <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Bestek 6.2.3</t>
+        </is>
+      </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Bestek 6.2.3</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r107</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r107</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6261,37 +6040,34 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="b">
-        <v>0</v>
-      </c>
+      <c r="S90" t="b">
+        <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Bestek 4.5.1</t>
+        </is>
+      </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Bestek 4.5.1</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r109</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r109</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6317,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -6325,32 +6101,29 @@
       <c r="L91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="b">
-        <v>0</v>
-      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>blauwe lamp</t>
+        </is>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>blauwe lamp</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r111</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r111</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6376,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -6384,32 +6157,29 @@
       <c r="L92" t="n">
         <v>0</v>
       </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="b">
-        <v>1</v>
-      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>levering derden</t>
+        </is>
+      </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>levering derden</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r113</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r113</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6435,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -6443,28 +6213,25 @@
       <c r="L93" t="n">
         <v>0</v>
       </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="b">
-        <v>0</v>
-      </c>
+      <c r="S93" t="b">
+        <v>0</v>
+      </c>
+      <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r114</t>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r114</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6490,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -6498,28 +6265,25 @@
       <c r="L94" t="n">
         <v>0</v>
       </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="b">
-        <v>0</v>
-      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r116</t>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r116</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6545,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -6553,28 +6317,25 @@
       <c r="L95" t="n">
         <v>0</v>
       </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="b">
-        <v>0</v>
-      </c>
+      <c r="S95" t="b">
+        <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r117</t>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r117</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6600,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -6608,28 +6369,25 @@
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="b">
-        <v>0</v>
-      </c>
+      <c r="S96" t="b">
+        <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r118</t>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r118</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6655,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -6663,28 +6421,25 @@
       <c r="L97" t="n">
         <v>0</v>
       </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="b">
-        <v>0</v>
-      </c>
+      <c r="S97" t="b">
+        <v>0</v>
+      </c>
+      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r119</t>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r119</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6713,37 +6468,34 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="b">
-        <v>0</v>
-      </c>
+      <c r="S98" t="b">
+        <v>0</v>
+      </c>
+      <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gele lamp</t>
+        </is>
+      </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Gele lamp</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r120</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r120</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6769,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -6777,32 +6529,29 @@
       <c r="L99" t="n">
         <v>0</v>
       </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="b">
-        <v>0</v>
-      </c>
+      <c r="S99" t="b">
+        <v>0</v>
+      </c>
+      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Bestek 4.2.10</t>
+        </is>
+      </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Bestek 4.2.10</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r121</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r121</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6828,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -6836,28 +6585,25 @@
       <c r="L100" t="n">
         <v>0</v>
       </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="b">
-        <v>0</v>
-      </c>
+      <c r="S100" t="b">
+        <v>0</v>
+      </c>
+      <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r122</t>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r122</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6883,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -6891,32 +6637,29 @@
       <c r="L101" t="n">
         <v>0</v>
       </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="b">
-        <v>0</v>
-      </c>
+      <c r="S101" t="b">
+        <v>0</v>
+      </c>
+      <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Bestek 4.4.1</t>
+        </is>
+      </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Bestek 4.4.1</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r123</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r123</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6942,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -6950,28 +6693,25 @@
       <c r="L102" t="n">
         <v>0</v>
       </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="b">
-        <v>0</v>
-      </c>
+      <c r="S102" t="b">
+        <v>0</v>
+      </c>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r124</t>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r124</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6997,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -7005,32 +6745,29 @@
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="b">
-        <v>1</v>
-      </c>
+      <c r="S103" t="b">
+        <v>1</v>
+      </c>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Bestek 4.2.1. Voeding vanuit E-installatie</t>
+        </is>
+      </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Bestek 4.2.1. Voeding vanuit E-installatie</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r125</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r125</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7068,36 +6805,33 @@
       <c r="L104" t="n">
         <v>0</v>
       </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="b">
-        <v>0</v>
-      </c>
+      <c r="S104" t="b">
+        <v>0</v>
+      </c>
+      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>24Vac/0-10VDC/0-50°C/0-100%</t>
+        </is>
+      </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>24Vac/0-10VDC/0-50°C/0-100%</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r127</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r127</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7135,28 +6869,25 @@
       <c r="L105" t="n">
         <v>0</v>
       </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="b">
-        <v>0</v>
-      </c>
+      <c r="S105" t="b">
+        <v>0</v>
+      </c>
+      <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r128</t>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r128</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7185,37 +6916,34 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="b">
-        <v>0</v>
-      </c>
+      <c r="S106" t="b">
+        <v>0</v>
+      </c>
+      <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>rode lamp</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>rode lamp</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r129</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r129</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7244,37 +6972,34 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="b">
-        <v>0</v>
-      </c>
+      <c r="S107" t="b">
+        <v>0</v>
+      </c>
+      <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>rode lamp</t>
+        </is>
+      </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>rode lamp</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r130</t>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r130</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7303,33 +7028,30 @@
         <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="b">
-        <v>0</v>
-      </c>
+      <c r="S108" t="b">
+        <v>0</v>
+      </c>
+      <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r131</t>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r131</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7352,39 +7074,40 @@
         <v>30</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J109" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="K109" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
-      <c r="M109" t="n">
-        <v>18</v>
-      </c>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="b">
-        <v>0</v>
-      </c>
+      <c r="S109" t="b">
+        <v>0</v>
+      </c>
+      <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r132</t>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r132</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7411,39 +7134,40 @@
         <v>30</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K110" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
-      <c r="M110" t="n">
-        <v>18</v>
-      </c>
-      <c r="N110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="b">
-        <v>0</v>
-      </c>
+      <c r="S110" t="b">
+        <v>0</v>
+      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r133</t>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r133</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7470,39 +7194,40 @@
         <v>3</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
-      <c r="M111" t="n">
-        <v>2</v>
-      </c>
-      <c r="N111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="b">
-        <v>0</v>
-      </c>
+      <c r="S111" t="b">
+        <v>0</v>
+      </c>
+      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r134</t>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r134</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>RK?</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7529,32 +7254,33 @@
         <v>33</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="K112" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
-      <c r="M112" t="n">
-        <v>20</v>
-      </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>BACnet-punten</t>
+        </is>
+      </c>
       <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="b">
-        <v>0</v>
-      </c>
+      <c r="S112" t="b">
+        <v>0</v>
+      </c>
+      <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>inputs\7268\IO_T.xlsx:Append1:r135</t>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>inputs\tested\7268\IO_T.xlsx:Append1:r135</t>
         </is>
       </c>
     </row>
